--- a/ig/DM-FEVRIER-2026/ASS-A28-TypeDiplome-Diplome-Profession-EPARS.xlsx
+++ b/ig/DM-FEVRIER-2026/ASS-A28-TypeDiplome-Diplome-Profession-EPARS.xlsx
@@ -156,7 +156,7 @@
     <t>DIP413</t>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/TRE_R58-AutreTypeDiplome/FHIR/TRE-R58-AutreTypeDiplome|20251222120000</t>
+    <t>https://mos.esante.gouv.fr/NOS/TRE_R58-AutreTypeDiplome/FHIR/TRE-R58-AutreTypeDiplome|20260223120000</t>
   </si>
   <si>
     <t>AU</t>
